--- a/pcb/af4-trigger-hat-BOM.xlsx
+++ b/pcb/af4-trigger-hat-BOM.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>LED, green, 2.0 V typ</t>
+          <t>LED, green, 2.2 V typ</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
